--- a/data/availability/projects/ora/zed-east.xlsx
+++ b/data/availability/projects/ora/zed-east.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zed East latest availability</t>
+          <t>Updated inventory for zed-east</t>
         </is>
       </c>
     </row>
@@ -570,14 +570,14 @@
         <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="H2" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -620,14 +620,14 @@
         <v>145</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>23.5</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>23.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -670,14 +670,14 @@
         <v>193</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>32.5</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>32.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -770,29 +770,29 @@
         <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>8.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>8.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -820,29 +820,29 @@
         <v>89</v>
       </c>
       <c r="G7" t="n">
-        <v>11.7</v>
+        <v>12.85</v>
       </c>
       <c r="H7" t="n">
-        <v>11.7</v>
+        <v>12.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -870,29 +870,29 @@
         <v>114</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>17.35</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>17.35</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -920,29 +920,29 @@
         <v>145</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1070,14 @@
         <v>270</v>
       </c>
       <c r="G12" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H12" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1211,25 +1211,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>86-93 sqm</t>
+          <t>86-93 SQM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12800000</v>
+        <v>13200000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1272,25 +1272,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>145 sqm</t>
+          <t>145 SQM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21000000</v>
+        <v>23500000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1333,25 +1333,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>193 sqm</t>
+          <t>193 SQM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>31000000</v>
+        <v>32500000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>300 sqm</t>
+          <t>300 SQM Loft</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ZE-CSR-STD</t>
+          <t>ZE-SRV-STD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1455,25 +1455,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>65 sqm</t>
+          <t>65 SQM Serviced Studio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8900000</v>
+        <v>9450000</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZE-CSR-SER-1BR</t>
+          <t>ZE-SRV-1BR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,25 +1516,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>86-92 sqm</t>
+          <t>86-92 SQM Serviced</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11700000</v>
+        <v>12850000</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZE-CSR-SER-2BR</t>
+          <t>ZE-SRV-2BR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1577,25 +1577,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>114 sqm</t>
+          <t>114 SQM Serviced</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16000000</v>
+        <v>17350000</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZE-CSR-SER-3BR</t>
+          <t>ZE-SRV-3BR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CSR Building C&amp;D (Serviced)</t>
+          <t>CSR Building C&amp;D</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1638,25 +1638,25 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>145 sqm</t>
+          <t>145 SQM Serviced</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>22000000</v>
+        <v>23500000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Serviced Apartments</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
+          <t>5%+5% – 10 years</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Duplex Upper 188 sqm</t>
+          <t>Duplex Upper 188 SQM</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ZE-EM-DUP-GND</t>
+          <t>ZE-EM-DUP-G</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Duplex Ground 191 sqm</t>
+          <t>Duplex Ground 191 SQM</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZE-EM-4PLEX</t>
+          <t>ZE-EM-FOUR-UP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1821,25 +1821,25 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fourplex Upper 174-206 sqm</t>
+          <t>Fourplex Upper 174-206 SQM</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29000000</v>
+        <v>31000000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Townhouse Middle 215 sqm</t>
+          <t>Townhouse Middle 215 SQM</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Townhouse Corner 215 sqm</t>
+          <t>Townhouse Corner 215 SQM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ZE-EM-VILLA</t>
+          <t>ZE-EM-SA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2004,25 +2004,25 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Standalone 250-290 sqm</t>
+          <t>Standalone 250-290 SQM</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>57000000</v>
+        <v>73000000</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phase 1 Q1 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5% DP + 5% after 3 months, installments over 8 years</t>
+          <t>5% + 5% – 8 years</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">

--- a/data/availability/projects/ora/zed-east.xlsx
+++ b/data/availability/projects/ora/zed-east.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for zed-east</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/ora/zed-east.xlsx
+++ b/data/availability/projects/ora/zed-east.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Q1 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
